--- a/05_DataDictionary.xlsx
+++ b/05_DataDictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tevitSecondYear\DataBase\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\dataBase\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738D7003-3685-43DE-92C8-C35D1F81FFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBF807A-1124-4E63-B447-8746338B1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="146" xr2:uid="{15F9293E-A5AC-4003-97B1-C6B8E3AFCC26}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="146" xr2:uid="{15F9293E-A5AC-4003-97B1-C6B8E3AFCC26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
   <si>
     <t>PK</t>
   </si>
@@ -247,6 +247,30 @@
   </si>
   <si>
     <t>(ตารางรายละเอียดบิล)</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Sellers(SellerID)</t>
+  </si>
+  <si>
+    <t>Employees(EmployeeID)</t>
+  </si>
+  <si>
+    <t>Purchases(PurchaseID)</t>
+  </si>
+  <si>
+    <t>Categories(CategoryID)</t>
+  </si>
+  <si>
+    <t>Materials(MaterialsID)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>ลำดับที่</t>
   </si>
 </sst>
 </file>
@@ -257,7 +281,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -414,14 +438,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>27709</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>110837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>937260</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>112339</xdr:rowOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>112340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -458,9 +482,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -498,7 +522,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -604,7 +628,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -746,7 +770,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -754,14 +778,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6A12BF-E431-4781-A510-2A2276AE6A04}">
-  <dimension ref="B2:H33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:I34"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="20.77734375" customWidth="1"/>
-    <col min="5" max="8" width="13.77734375" customWidth="1"/>
+    <col min="2" max="4" width="20.796875" customWidth="1"/>
+    <col min="5" max="8" width="13.796875" customWidth="1"/>
+    <col min="9" max="9" width="21.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -770,18 +795,20 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="6"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="9"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -803,8 +830,11 @@
       <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -824,8 +854,9 @@
       <c r="H5" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>68</v>
       </c>
@@ -843,8 +874,9 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -860,8 +892,9 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
         <v>15</v>
@@ -879,8 +912,9 @@
         <v>67</v>
       </c>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -898,8 +932,9 @@
         <v>67</v>
       </c>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
         <v>17</v>
@@ -917,8 +952,9 @@
         <v>67</v>
       </c>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -936,8 +972,9 @@
         <v>67</v>
       </c>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
         <v>19</v>
@@ -955,8 +992,9 @@
         <v>67</v>
       </c>
       <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -974,8 +1012,9 @@
         <v>67</v>
       </c>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
@@ -995,8 +1034,9 @@
       <c r="H14" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>69</v>
       </c>
@@ -1014,8 +1054,9 @@
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -1035,8 +1076,9 @@
       <c r="H16" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>70</v>
       </c>
@@ -1056,8 +1098,11 @@
       <c r="H17" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
         <v>38</v>
@@ -1073,8 +1118,9 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
         <v>39</v>
@@ -1090,8 +1136,9 @@
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
         <v>40</v>
@@ -1107,8 +1154,9 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
@@ -1128,8 +1176,9 @@
       <c r="H21" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>71</v>
       </c>
@@ -1147,8 +1196,9 @@
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -1166,8 +1216,9 @@
         <v>67</v>
       </c>
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
@@ -1187,8 +1238,9 @@
       <c r="H24" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>72</v>
       </c>
@@ -1208,8 +1260,11 @@
       <c r="H25" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
         <v>12</v>
@@ -1227,8 +1282,11 @@
       <c r="H26" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="I26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
         <v>46</v>
@@ -1244,8 +1302,9 @@
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
         <v>47</v>
@@ -1261,8 +1320,9 @@
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="2:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>48</v>
       </c>
@@ -1282,69 +1342,79 @@
       <c r="H29" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" s="1">
         <v>5</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="H31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F32" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="2:8" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>30</v>
@@ -1354,11 +1424,30 @@
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" ht="23.4" x14ac:dyDescent="0.25">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
